--- a/xlsx/packagedata20260412-2 singletypepkg stackable cn.xlsx
+++ b/xlsx/packagedata20260412-2 singletypepkg stackable cn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56E836E-6DF7-4B14-A2C4-095030AF1FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745617D2-ED4E-436B-B464-D8D2C94EA039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -502,7 +502,7 @@
         <v>71</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>200</v>
@@ -531,13 +531,13 @@
         <v>110</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>71</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>300</v>
